--- a/artfynd/A 45604-2023 artfynd.xlsx
+++ b/artfynd/A 45604-2023 artfynd.xlsx
@@ -1656,10 +1656,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118036763</v>
+        <v>118036851</v>
       </c>
       <c r="B10" t="n">
-        <v>97857</v>
+        <v>97756</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1672,32 +1672,28 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>223597</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -1708,10 +1704,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>573147</v>
+        <v>573148</v>
       </c>
       <c r="R10" t="n">
-        <v>6784180</v>
+        <v>6784152</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1743,7 +1739,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1753,7 +1749,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1781,10 +1777,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118036851</v>
+        <v>118036763</v>
       </c>
       <c r="B11" t="n">
-        <v>97756</v>
+        <v>97857</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1797,28 +1793,32 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223597</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>573148</v>
+        <v>573147</v>
       </c>
       <c r="R11" t="n">
-        <v>6784152</v>
+        <v>6784180</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 45604-2023 artfynd.xlsx
+++ b/artfynd/A 45604-2023 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>118036975</v>
       </c>
       <c r="B6" t="n">
-        <v>96797</v>
+        <v>96799</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>117708597</v>
       </c>
       <c r="B8" t="n">
-        <v>97754</v>
+        <v>97756</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118036882</v>
+        <v>118036851</v>
       </c>
       <c r="B9" t="n">
-        <v>97859</v>
+        <v>97758</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1547,26 +1547,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>223597</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1583,10 +1579,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573036</v>
+        <v>573148</v>
       </c>
       <c r="R9" t="n">
-        <v>6784083</v>
+        <v>6784152</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1618,7 +1614,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1628,7 +1624,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1656,10 +1652,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118036851</v>
+        <v>118036882</v>
       </c>
       <c r="B10" t="n">
-        <v>97756</v>
+        <v>97861</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1672,22 +1668,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223597</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>573148</v>
+        <v>573036</v>
       </c>
       <c r="R10" t="n">
-        <v>6784152</v>
+        <v>6784083</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1780,7 +1780,7 @@
         <v>118036763</v>
       </c>
       <c r="B11" t="n">
-        <v>97857</v>
+        <v>97859</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>118036809</v>
       </c>
       <c r="B12" t="n">
-        <v>97756</v>
+        <v>97758</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 45604-2023 artfynd.xlsx
+++ b/artfynd/A 45604-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1649,10 +1649,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117375884</v>
+        <v>120256881</v>
       </c>
       <c r="B10" t="n">
-        <v>97859</v>
+        <v>97907</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1661,34 +1661,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1697,13 +1701,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>573036</v>
+        <v>572999</v>
       </c>
       <c r="R10" t="n">
-        <v>6784076</v>
+        <v>6783716</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1727,22 +1731,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1770,10 +1774,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117708597</v>
+        <v>120256815</v>
       </c>
       <c r="B11" t="n">
-        <v>97758</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1782,36 +1786,36 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223591</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1822,13 +1826,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>573036</v>
+        <v>572911</v>
       </c>
       <c r="R11" t="n">
-        <v>6784076</v>
+        <v>6783683</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1852,7 +1856,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1862,7 +1866,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1895,10 +1899,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118036851</v>
+        <v>117375884</v>
       </c>
       <c r="B12" t="n">
-        <v>97766</v>
+        <v>97859</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1911,30 +1915,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223597</v>
+        <v>219847</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1943,13 +1947,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>573148</v>
+        <v>573036</v>
       </c>
       <c r="R12" t="n">
-        <v>6784152</v>
+        <v>6784076</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1973,22 +1977,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2016,10 +2020,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118036809</v>
+        <v>117708597</v>
       </c>
       <c r="B13" t="n">
-        <v>97766</v>
+        <v>97758</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2032,22 +2036,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223597</v>
+        <v>223591</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -2064,13 +2072,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>573141</v>
+        <v>573036</v>
       </c>
       <c r="R13" t="n">
-        <v>6784172</v>
+        <v>6784076</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2094,22 +2102,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2137,10 +2145,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118036763</v>
+        <v>118036851</v>
       </c>
       <c r="B14" t="n">
-        <v>97867</v>
+        <v>97766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2153,32 +2161,28 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>223597</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -2189,10 +2193,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>573147</v>
+        <v>573148</v>
       </c>
       <c r="R14" t="n">
-        <v>6784180</v>
+        <v>6784152</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2224,7 +2228,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2234,7 +2238,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2262,10 +2266,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118036882</v>
+        <v>118036809</v>
       </c>
       <c r="B15" t="n">
-        <v>97869</v>
+        <v>97766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2278,26 +2282,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219847</v>
+        <v>223597</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>573036</v>
+        <v>573141</v>
       </c>
       <c r="R15" t="n">
-        <v>6784083</v>
+        <v>6784172</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2384,6 +2384,256 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>118036763</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97867</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Söråsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>573147</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6784180</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>118036882</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97869</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Söråsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>573036</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6784083</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45604-2023 artfynd.xlsx
+++ b/artfynd/A 45604-2023 artfynd.xlsx
@@ -1652,7 +1652,7 @@
         <v>120256881</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>120256815</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 45604-2023 artfynd.xlsx
+++ b/artfynd/A 45604-2023 artfynd.xlsx
@@ -1649,7 +1649,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120256881</v>
+        <v>120256815</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572999</v>
+        <v>572911</v>
       </c>
       <c r="R10" t="n">
-        <v>6783716</v>
+        <v>6783683</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1774,7 +1774,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120256815</v>
+        <v>120256881</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572911</v>
+        <v>572999</v>
       </c>
       <c r="R11" t="n">
-        <v>6783683</v>
+        <v>6783716</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 45604-2023 artfynd.xlsx
+++ b/artfynd/A 45604-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1899,10 +1899,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117375884</v>
+        <v>120463543</v>
       </c>
       <c r="B12" t="n">
-        <v>97859</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1911,32 +1911,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1947,13 +1943,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>573036</v>
+        <v>572996</v>
       </c>
       <c r="R12" t="n">
-        <v>6784076</v>
+        <v>6783897</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1977,22 +1973,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2001,29 +1997,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Torbjörn Alsing</t>
+          <t>Anita Olsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Torbjörn Alsing</t>
+          <t>Anita Olsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117708597</v>
+        <v>120463539</v>
       </c>
       <c r="B13" t="n">
-        <v>97758</v>
+        <v>57431</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2036,35 +2031,35 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223591</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2072,13 +2067,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>573036</v>
+        <v>572996</v>
       </c>
       <c r="R13" t="n">
-        <v>6784076</v>
+        <v>6783897</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2102,22 +2097,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2126,29 +2121,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Torbjörn Alsing</t>
+          <t>Anita Olsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Torbjörn Alsing</t>
+          <t>Anita Olsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118036851</v>
+        <v>117375884</v>
       </c>
       <c r="B14" t="n">
-        <v>97766</v>
+        <v>97859</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2161,30 +2155,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>223597</v>
+        <v>219847</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2193,13 +2187,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>573148</v>
+        <v>573036</v>
       </c>
       <c r="R14" t="n">
-        <v>6784152</v>
+        <v>6784076</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2223,22 +2217,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2266,10 +2260,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118036809</v>
+        <v>117708597</v>
       </c>
       <c r="B15" t="n">
-        <v>97766</v>
+        <v>97758</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2282,22 +2276,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223597</v>
+        <v>223591</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2314,13 +2312,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>573141</v>
+        <v>573036</v>
       </c>
       <c r="R15" t="n">
-        <v>6784172</v>
+        <v>6784076</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2344,22 +2342,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2387,10 +2385,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118036763</v>
+        <v>118036851</v>
       </c>
       <c r="B16" t="n">
-        <v>97867</v>
+        <v>97766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2403,32 +2401,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>223597</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -2439,10 +2433,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>573147</v>
+        <v>573148</v>
       </c>
       <c r="R16" t="n">
-        <v>6784180</v>
+        <v>6784152</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2474,7 +2468,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2484,7 +2478,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2512,10 +2506,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118036882</v>
+        <v>118036809</v>
       </c>
       <c r="B17" t="n">
-        <v>97869</v>
+        <v>97766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2528,26 +2522,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219847</v>
+        <v>223597</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2564,10 +2554,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>573036</v>
+        <v>573141</v>
       </c>
       <c r="R17" t="n">
-        <v>6784083</v>
+        <v>6784172</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2599,7 +2589,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2609,7 +2599,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2634,6 +2624,256 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>118036763</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97867</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Söråsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>573147</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6784180</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>118036882</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97869</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Söråsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>573036</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6784083</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45604-2023 artfynd.xlsx
+++ b/artfynd/A 45604-2023 artfynd.xlsx
@@ -1899,10 +1899,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120463543</v>
+        <v>120463539</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>57431</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1911,31 +1911,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1978,7 +1986,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1988,7 +1996,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2015,10 +2023,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120463539</v>
+        <v>120463543</v>
       </c>
       <c r="B13" t="n">
-        <v>57431</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2027,39 +2035,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 45604-2023 artfynd.xlsx
+++ b/artfynd/A 45604-2023 artfynd.xlsx
@@ -1899,10 +1899,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120463539</v>
+        <v>120463543</v>
       </c>
       <c r="B12" t="n">
-        <v>57431</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1911,39 +1911,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1986,7 +1978,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1996,7 +1988,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2023,10 +2015,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120463543</v>
+        <v>120463539</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>57431</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2035,31 +2027,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 45604-2023 artfynd.xlsx
+++ b/artfynd/A 45604-2023 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>116960855</v>
       </c>
       <c r="B2" t="n">
-        <v>57278</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -806,11 +806,11 @@
         <v>117381194</v>
       </c>
       <c r="B3" t="n">
-        <v>57398</v>
+        <v>57589</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1167,11 +1167,11 @@
         <v>118037037</v>
       </c>
       <c r="B6" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2018,11 +2018,11 @@
         <v>120463539</v>
       </c>
       <c r="B13" t="n">
-        <v>57455</v>
+        <v>57589</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">

--- a/artfynd/A 45604-2023 artfynd.xlsx
+++ b/artfynd/A 45604-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2139,10 +2139,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117375884</v>
+        <v>123167613</v>
       </c>
       <c r="B14" t="n">
-        <v>97859</v>
+        <v>98365</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2151,30 +2151,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2187,13 +2187,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>573036</v>
+        <v>572907</v>
       </c>
       <c r="R14" t="n">
-        <v>6784076</v>
+        <v>6783930</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2217,22 +2217,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:40</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2253,17 +2243,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Torbjörn Alsing</t>
+          <t>Torbjörn Alsing, Stefan Olander, Per-Erik Modd</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117708597</v>
+        <v>123167615</v>
       </c>
       <c r="B15" t="n">
-        <v>97758</v>
+        <v>98365</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2272,38 +2262,34 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223591</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2312,13 +2298,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>573036</v>
+        <v>572855</v>
       </c>
       <c r="R15" t="n">
-        <v>6784076</v>
+        <v>6783900</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2342,22 +2328,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2378,17 +2354,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Torbjörn Alsing</t>
+          <t>Torbjörn Alsing, Stefan Olander, Per-Erik Modd</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118036851</v>
+        <v>117375884</v>
       </c>
       <c r="B16" t="n">
-        <v>97766</v>
+        <v>97859</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2401,30 +2377,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>223597</v>
+        <v>219847</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -2433,13 +2409,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>573148</v>
+        <v>573036</v>
       </c>
       <c r="R16" t="n">
-        <v>6784152</v>
+        <v>6784076</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2463,22 +2439,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2506,10 +2482,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118036809</v>
+        <v>117708597</v>
       </c>
       <c r="B17" t="n">
-        <v>97766</v>
+        <v>97758</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2522,22 +2498,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>223597</v>
+        <v>223591</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2554,13 +2534,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>573141</v>
+        <v>573036</v>
       </c>
       <c r="R17" t="n">
-        <v>6784172</v>
+        <v>6784076</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2584,22 +2564,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2627,10 +2607,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118036763</v>
+        <v>118036851</v>
       </c>
       <c r="B18" t="n">
-        <v>97867</v>
+        <v>97766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2643,32 +2623,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>223597</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -2679,10 +2655,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>573147</v>
+        <v>573148</v>
       </c>
       <c r="R18" t="n">
-        <v>6784180</v>
+        <v>6784152</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2714,7 +2690,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2724,7 +2700,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2752,10 +2728,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118036882</v>
+        <v>118036809</v>
       </c>
       <c r="B19" t="n">
-        <v>97869</v>
+        <v>97766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2768,26 +2744,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219847</v>
+        <v>223597</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2804,10 +2776,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>573036</v>
+        <v>573141</v>
       </c>
       <c r="R19" t="n">
-        <v>6784083</v>
+        <v>6784172</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2839,7 +2811,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2849,7 +2821,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2874,6 +2846,367 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>118036763</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97867</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Söråsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>573147</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6784180</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>118036882</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97869</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Söråsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>573036</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6784083</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>123167649</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Knärot, Hls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>573118</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6783904</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing, Stefan Olander, Per-Erik Modd</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45604-2023 artfynd.xlsx
+++ b/artfynd/A 45604-2023 artfynd.xlsx
@@ -2139,7 +2139,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123167613</v>
+        <v>123167615</v>
       </c>
       <c r="B14" t="n">
         <v>98365</v>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572907</v>
+        <v>572855</v>
       </c>
       <c r="R14" t="n">
-        <v>6783930</v>
+        <v>6783900</v>
       </c>
       <c r="S14" t="n">
         <v>100</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123167615</v>
+        <v>123167613</v>
       </c>
       <c r="B15" t="n">
         <v>98365</v>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572855</v>
+        <v>572907</v>
       </c>
       <c r="R15" t="n">
-        <v>6783900</v>
+        <v>6783930</v>
       </c>
       <c r="S15" t="n">
         <v>100</v>

--- a/artfynd/A 45604-2023 artfynd.xlsx
+++ b/artfynd/A 45604-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>116960855</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>117381194</v>
       </c>
       <c r="B3" t="n">
-        <v>57589</v>
+        <v>57592</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>118037037</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>120463539</v>
       </c>
       <c r="B13" t="n">
-        <v>57589</v>
+        <v>57592</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123167615</v>
+        <v>123167613</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572855</v>
+        <v>572907</v>
       </c>
       <c r="R14" t="n">
-        <v>6783900</v>
+        <v>6783930</v>
       </c>
       <c r="S14" t="n">
         <v>100</v>
@@ -2250,10 +2250,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123167613</v>
+        <v>123167615</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572907</v>
+        <v>572855</v>
       </c>
       <c r="R15" t="n">
-        <v>6783930</v>
+        <v>6783900</v>
       </c>
       <c r="S15" t="n">
         <v>100</v>
@@ -3102,7 +3102,7 @@
         <v>123167649</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 45604-2023 artfynd.xlsx
+++ b/artfynd/A 45604-2023 artfynd.xlsx
@@ -2139,10 +2139,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123167613</v>
+        <v>123167615</v>
       </c>
       <c r="B14" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572907</v>
+        <v>572855</v>
       </c>
       <c r="R14" t="n">
-        <v>6783930</v>
+        <v>6783900</v>
       </c>
       <c r="S14" t="n">
         <v>100</v>
@@ -2250,10 +2250,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123167615</v>
+        <v>123167613</v>
       </c>
       <c r="B15" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572855</v>
+        <v>572907</v>
       </c>
       <c r="R15" t="n">
-        <v>6783900</v>
+        <v>6783930</v>
       </c>
       <c r="S15" t="n">
         <v>100</v>
@@ -3102,7 +3102,7 @@
         <v>123167649</v>
       </c>
       <c r="B22" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 45604-2023 artfynd.xlsx
+++ b/artfynd/A 45604-2023 artfynd.xlsx
@@ -2142,7 +2142,7 @@
         <v>123167615</v>
       </c>
       <c r="B14" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>123167613</v>
       </c>
       <c r="B15" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>123167649</v>
       </c>
       <c r="B22" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 45604-2023 artfynd.xlsx
+++ b/artfynd/A 45604-2023 artfynd.xlsx
@@ -2139,10 +2139,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123167615</v>
+        <v>123167613</v>
       </c>
       <c r="B14" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572855</v>
+        <v>572907</v>
       </c>
       <c r="R14" t="n">
-        <v>6783900</v>
+        <v>6783930</v>
       </c>
       <c r="S14" t="n">
         <v>100</v>
@@ -2250,10 +2250,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123167613</v>
+        <v>123167615</v>
       </c>
       <c r="B15" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572907</v>
+        <v>572855</v>
       </c>
       <c r="R15" t="n">
-        <v>6783930</v>
+        <v>6783900</v>
       </c>
       <c r="S15" t="n">
         <v>100</v>
@@ -3102,7 +3102,7 @@
         <v>123167649</v>
       </c>
       <c r="B22" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 45604-2023 artfynd.xlsx
+++ b/artfynd/A 45604-2023 artfynd.xlsx
@@ -2142,7 +2142,7 @@
         <v>123167613</v>
       </c>
       <c r="B14" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>123167615</v>
       </c>
       <c r="B15" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>123167649</v>
       </c>
       <c r="B22" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 45604-2023 artfynd.xlsx
+++ b/artfynd/A 45604-2023 artfynd.xlsx
@@ -2139,10 +2139,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123167613</v>
+        <v>123167615</v>
       </c>
       <c r="B14" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572907</v>
+        <v>572855</v>
       </c>
       <c r="R14" t="n">
-        <v>6783930</v>
+        <v>6783900</v>
       </c>
       <c r="S14" t="n">
         <v>100</v>
@@ -2250,10 +2250,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123167615</v>
+        <v>123167613</v>
       </c>
       <c r="B15" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572855</v>
+        <v>572907</v>
       </c>
       <c r="R15" t="n">
-        <v>6783900</v>
+        <v>6783930</v>
       </c>
       <c r="S15" t="n">
         <v>100</v>
@@ -3102,7 +3102,7 @@
         <v>123167649</v>
       </c>
       <c r="B22" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 45604-2023 artfynd.xlsx
+++ b/artfynd/A 45604-2023 artfynd.xlsx
@@ -2142,7 +2142,7 @@
         <v>123167615</v>
       </c>
       <c r="B14" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>123167613</v>
       </c>
       <c r="B15" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>123167649</v>
       </c>
       <c r="B22" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 45604-2023 artfynd.xlsx
+++ b/artfynd/A 45604-2023 artfynd.xlsx
@@ -2250,10 +2250,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123167613</v>
+        <v>123168049</v>
       </c>
       <c r="B15" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>6783930</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>

--- a/artfynd/A 45604-2023 artfynd.xlsx
+++ b/artfynd/A 45604-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2361,15 +2361,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117375884</v>
+        <v>126373202</v>
       </c>
       <c r="B16" t="n">
-        <v>97859</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,28 +2372,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -2409,10 +2400,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>573036</v>
+        <v>573007</v>
       </c>
       <c r="R16" t="n">
-        <v>6784076</v>
+        <v>6784115</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2439,22 +2430,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:40</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2470,27 +2451,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Torbjörn Alsing</t>
+          <t>Mattias Lindholm</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Torbjörn Alsing</t>
+          <t>Mattias Lindholm</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117708597</v>
+        <v>126373190</v>
       </c>
       <c r="B17" t="n">
-        <v>97758</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98375</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,34 +2474,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2534,10 +2502,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>573036</v>
+        <v>573007</v>
       </c>
       <c r="R17" t="n">
-        <v>6784076</v>
+        <v>6784115</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2564,22 +2532,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2595,27 +2553,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Torbjörn Alsing</t>
+          <t>Mattias Lindholm</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Torbjörn Alsing</t>
+          <t>Mattias Lindholm</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118036851</v>
+        <v>126373232</v>
       </c>
       <c r="B18" t="n">
-        <v>97766</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98386</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2623,30 +2576,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>223597</v>
+        <v>219874</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2655,13 +2604,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>573148</v>
+        <v>573007</v>
       </c>
       <c r="R18" t="n">
-        <v>6784152</v>
+        <v>6784115</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2685,22 +2634,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2716,27 +2655,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Torbjörn Alsing</t>
+          <t>Mattias Lindholm</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Torbjörn Alsing</t>
+          <t>Mattias Lindholm</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118036809</v>
+        <v>126373197</v>
       </c>
       <c r="B19" t="n">
-        <v>97766</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2744,30 +2678,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223597</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2776,13 +2706,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>573141</v>
+        <v>573007</v>
       </c>
       <c r="R19" t="n">
-        <v>6784172</v>
+        <v>6784115</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2806,22 +2736,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:10</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:10</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2837,22 +2757,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Torbjörn Alsing</t>
+          <t>Mattias Lindholm</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Torbjörn Alsing</t>
+          <t>Mattias Lindholm</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118036763</v>
+        <v>117375884</v>
       </c>
       <c r="B20" t="n">
-        <v>97867</v>
+        <v>97859</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2865,34 +2785,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2901,13 +2817,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>573147</v>
+        <v>573036</v>
       </c>
       <c r="R20" t="n">
-        <v>6784180</v>
+        <v>6784076</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2931,22 +2847,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2974,10 +2890,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118036882</v>
+        <v>117708597</v>
       </c>
       <c r="B21" t="n">
-        <v>97869</v>
+        <v>97758</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2990,26 +2906,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -3029,10 +2945,10 @@
         <v>573036</v>
       </c>
       <c r="R21" t="n">
-        <v>6784083</v>
+        <v>6784076</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3056,22 +2972,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3099,10 +3015,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123167649</v>
+        <v>118036851</v>
       </c>
       <c r="B22" t="n">
-        <v>98504</v>
+        <v>97766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3111,46 +3027,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>223597</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Knärot, Hls</t>
+          <t>Söråsen, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>573118</v>
+        <v>573148</v>
       </c>
       <c r="R22" t="n">
-        <v>6783904</v>
+        <v>6784152</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3177,12 +3093,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3203,10 +3129,492 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>118036809</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97766</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Söråsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>573141</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6784172</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>118036763</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97867</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Söråsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>573147</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6784180</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>118036882</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97869</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Söråsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>573036</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6784083</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>123167649</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Knärot, Hls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>573118</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6783904</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Torbjörn Alsing</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
           <t>Torbjörn Alsing, Stefan Olander, Per-Erik Modd</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45604-2023 artfynd.xlsx
+++ b/artfynd/A 45604-2023 artfynd.xlsx
@@ -2364,7 +2364,7 @@
         <v>126373202</v>
       </c>
       <c r="B16" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>126373190</v>
       </c>
       <c r="B17" t="n">
-        <v>98375</v>
+        <v>98384</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>126373232</v>
       </c>
       <c r="B18" t="n">
-        <v>98386</v>
+        <v>98395</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>126373197</v>
       </c>
       <c r="B19" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
